--- a/AssetName_CC.xlsx
+++ b/AssetName_CC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H521045\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E39C98-9E8D-4429-9362-2F67ED2E5421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A3662-6F65-4A44-BBC8-8FCAC3B03FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="778" xr2:uid="{94F25FEC-704D-4839-92DF-5905A03E7CB4}"/>
   </bookViews>
@@ -1898,7 +1898,7 @@
   </sheetData>
   <autoFilter ref="B13:D85" xr:uid="{1FD7BCCC-7AE5-4193-9499-D5EAAA6E5874}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{8098FF77-7A8A-457E-ABB6-AD0C376608F8}">
       <formula1>"°C,°F,°K,°R"</formula1>
     </dataValidation>
@@ -1923,6 +1923,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:D85" xr:uid="{148BDB64-5490-47AA-AEDC-FB6CC3B9348F}">
       <formula1>"mole fraction, mole %"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3" xr:uid="{C8ADE76C-7D5A-424E-9D9E-E2E697875CAB}">
+      <formula1>"%,fraction"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1930,14 +1933,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b35d6b74-6782-4beb-83c2-7fe6ce0e43d8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ab989b8-44fb-4be9-9ba7-c9d978160c90" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2130,21 +2131,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b35d6b74-6782-4beb-83c2-7fe6ce0e43d8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ab989b8-44fb-4be9-9ba7-c9d978160c90" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6DBF745-3636-4FB1-8F8E-E0C3D4F2726B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2491A6CE-317B-4F7F-82CE-EEBA5ED2F099}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b35d6b74-6782-4beb-83c2-7fe6ce0e43d8"/>
-    <ds:schemaRef ds:uri="5ab989b8-44fb-4be9-9ba7-c9d978160c90"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2169,9 +2169,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2491A6CE-317B-4F7F-82CE-EEBA5ED2F099}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6DBF745-3636-4FB1-8F8E-E0C3D4F2726B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b35d6b74-6782-4beb-83c2-7fe6ce0e43d8"/>
+    <ds:schemaRef ds:uri="5ab989b8-44fb-4be9-9ba7-c9d978160c90"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
